--- a/jpcore-r4/develop/ValueSet-jp-condition-severity-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-severity-vs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>copyright HL7 Japan (出典：HL7-0421) LocalDefinition</t>
+    <t>Copyright HL7 Japan (出典：HL7-0421) LocalDefinition</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-severity-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-severity-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>
